--- a/Result/profitability/4737.xlsx
+++ b/Result/profitability/4737.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM71"/>
+  <dimension ref="A1:AM72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.87</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.545</v>
+        <v>-0.52125</v>
       </c>
       <c r="N2" t="n">
-        <v>35.48625</v>
+        <v>35.58125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.38</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2625000000000001</v>
+        <v>-0.2825</v>
       </c>
       <c r="N3" t="n">
-        <v>36.28125</v>
+        <v>36.39250000000001</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.98</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.07375000000000004</v>
+        <v>-0.13375</v>
       </c>
       <c r="N4" t="n">
-        <v>37.53875</v>
+        <v>37.52</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.99</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07624999999999996</v>
+        <v>0.01999999999999996</v>
       </c>
       <c r="N5" t="n">
-        <v>38.50625</v>
+        <v>39.11875</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.9</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3437499999999999</v>
+        <v>0.3699999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>41.1925</v>
+        <v>42.415</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.61</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5325</v>
+        <v>0.61875</v>
       </c>
       <c r="N7" t="n">
-        <v>43.97</v>
+        <v>43.68375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.98</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8274999999999999</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>45.3275</v>
+        <v>46.215</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9449,6 +9449,133 @@
       </c>
       <c r="AM71" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>4737</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>427</v>
+      </c>
+      <c r="D72" t="n">
+        <v>268</v>
+      </c>
+      <c r="E72" t="n">
+        <v>159</v>
+      </c>
+      <c r="F72" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="G72" t="n">
+        <v>-52</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-12.30%</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>-12</v>
+      </c>
+      <c r="J72" t="n">
+        <v>-65</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-53</v>
+      </c>
+      <c r="L72" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="M72" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="N72" t="n">
+        <v>34.64625</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W72" t="n">
+        <v>0.4000000000000001</v>
+      </c>
+      <c r="X72" t="n">
+        <v>-0.3669724770642203</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>7.100000000000001</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>0.2353331123632747</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>4.900000000000006</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>0.1513747296879828</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK72" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
